--- a/prix/push.xlsx
+++ b/prix/push.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94C41EE-88F6-4B3F-9699-3632CF0CA25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BF8E2B-17E3-42E9-8589-E962B6B24B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{37F12267-615D-4EAF-9E58-766BB65D19FA}"/>
   </bookViews>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -928,7 +928,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="10">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="10">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1319,7 +1319,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1439,7 +1439,7 @@
         <v>58</v>
       </c>
       <c r="F31" s="10">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1499,7 +1499,7 @@
         <v>64</v>
       </c>
       <c r="F34" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1519,7 +1519,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1539,7 +1539,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="10">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/push.xlsx
+++ b/prix/push.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BF8E2B-17E3-42E9-8589-E962B6B24B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C91C743-C019-4629-8B46-68AABDAB5DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{37F12267-615D-4EAF-9E58-766BB65D19FA}"/>
   </bookViews>
@@ -466,10 +466,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -861,14 +861,14 @@
       <c r="C2" s="8">
         <v>15</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>2.77</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>7</v>
+      <c r="F2" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -881,13 +881,13 @@
       <c r="C3" s="8">
         <v>16</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>3.7600000000000002</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <v>0</v>
       </c>
     </row>
@@ -901,13 +901,13 @@
       <c r="C4" s="8">
         <v>20</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>5.34</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <v>9</v>
       </c>
     </row>
@@ -921,14 +921,14 @@
       <c r="C5" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>6.32</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10">
-        <v>21</v>
+      <c r="F5" s="11">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -941,13 +941,13 @@
       <c r="C6" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>6.32</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>36</v>
       </c>
     </row>
@@ -961,13 +961,13 @@
       <c r="C7" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>7.48</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <v>9</v>
       </c>
     </row>
@@ -981,13 +981,13 @@
       <c r="C8" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>6</v>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
       <c r="C9" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>7.87</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>13</v>
       </c>
     </row>
@@ -1018,14 +1018,14 @@
       <c r="C10" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>5.78</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="10">
-        <v>32</v>
+      <c r="F10" s="11">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1038,13 +1038,13 @@
       <c r="C11" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>5.22</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>27</v>
       </c>
     </row>
@@ -1055,13 +1055,13 @@
       <c r="C12" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>8.4600000000000009</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>25</v>
       </c>
     </row>
@@ -1072,13 +1072,13 @@
       <c r="C13" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>9.370000000000001</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="11">
         <v>25</v>
       </c>
     </row>
@@ -1092,13 +1092,13 @@
       <c r="C14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>3.96</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>41</v>
       </c>
     </row>
@@ -1112,14 +1112,14 @@
       <c r="C15" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>4.16</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="10">
-        <v>21</v>
+      <c r="F15" s="11">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1132,13 +1132,13 @@
       <c r="C16" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>8.91</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="11">
         <v>11</v>
       </c>
     </row>
@@ -1152,13 +1152,13 @@
       <c r="C17" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <v>7.04</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="11">
         <v>17</v>
       </c>
     </row>
@@ -1172,13 +1172,13 @@
       <c r="C18" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <v>5.12</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="11">
         <v>49</v>
       </c>
     </row>
@@ -1192,13 +1192,13 @@
       <c r="C19" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>10.14</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="11">
         <v>26</v>
       </c>
     </row>
@@ -1212,13 +1212,13 @@
       <c r="C20" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <v>7.18</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="11">
         <v>21</v>
       </c>
     </row>
@@ -1232,13 +1232,13 @@
       <c r="C21" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>12.89</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="11">
         <v>8</v>
       </c>
     </row>
@@ -1252,14 +1252,14 @@
       <c r="C22" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <v>9.6</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="10">
-        <v>18</v>
+      <c r="F22" s="11">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1272,13 +1272,13 @@
       <c r="C23" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>13.1</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="11">
         <v>9</v>
       </c>
     </row>
@@ -1292,13 +1292,13 @@
       <c r="C24" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <v>9.58</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="11">
         <v>32</v>
       </c>
     </row>
@@ -1312,13 +1312,13 @@
       <c r="C25" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>8.1300000000000008</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1332,13 +1332,13 @@
       <c r="C26" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <v>14.68</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="11">
         <v>8</v>
       </c>
     </row>
@@ -1352,14 +1352,14 @@
       <c r="C27" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>6.24</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="10">
-        <v>44</v>
+      <c r="F27" s="11">
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1372,13 +1372,13 @@
       <c r="C28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <v>7.11</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="11">
         <v>10</v>
       </c>
     </row>
@@ -1392,13 +1392,13 @@
       <c r="C29" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <v>6.59</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="11">
         <v>18</v>
       </c>
     </row>
@@ -1412,13 +1412,13 @@
       <c r="C30" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <v>10.78</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="11">
         <v>7</v>
       </c>
     </row>
@@ -1432,13 +1432,13 @@
       <c r="C31" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <v>7.36</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="11">
         <v>34</v>
       </c>
     </row>
@@ -1452,13 +1452,13 @@
       <c r="C32" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <v>10.78</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1472,13 +1472,13 @@
       <c r="C33" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>17.32</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="11">
         <v>30</v>
       </c>
     </row>
@@ -1492,13 +1492,13 @@
       <c r="C34" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <v>0.83000000000000007</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="11">
         <v>12</v>
       </c>
     </row>
@@ -1512,14 +1512,14 @@
       <c r="C35" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <v>3.1</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="10">
-        <v>3</v>
+      <c r="F35" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1532,14 +1532,14 @@
       <c r="C36" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <v>1.95</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="10">
-        <v>25</v>
+      <c r="F36" s="11">
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1552,13 +1552,13 @@
       <c r="C37" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>3.15</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="11">
         <v>62</v>
       </c>
     </row>
@@ -1572,13 +1572,13 @@
       <c r="C38" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <v>11.4</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="11">
         <v>15</v>
       </c>
     </row>
@@ -1592,13 +1592,13 @@
       <c r="C39" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <v>10.01</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="11">
         <v>10</v>
       </c>
     </row>
@@ -1612,13 +1612,13 @@
       <c r="C40" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <v>10</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="11">
         <v>40</v>
       </c>
     </row>

--- a/prix/push.xlsx
+++ b/prix/push.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C91C743-C019-4629-8B46-68AABDAB5DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57C8812-A73A-44DD-A6C0-D816421639A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{37F12267-615D-4EAF-9E58-766BB65D19FA}"/>
   </bookViews>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -928,7 +928,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="11">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1359,7 +1359,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="11">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1539,7 +1539,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/push.xlsx
+++ b/prix/push.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57C8812-A73A-44DD-A6C0-D816421639A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573844AB-A392-4EBE-B116-D79D882D0B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{37F12267-615D-4EAF-9E58-766BB65D19FA}"/>
   </bookViews>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1008,7 +1008,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1199,7 +1199,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="11">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1359,7 +1359,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1439,7 +1439,7 @@
         <v>58</v>
       </c>
       <c r="F31" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1479,7 +1479,7 @@
         <v>62</v>
       </c>
       <c r="F33" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1519,7 +1519,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1539,7 +1539,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="11">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1559,7 +1559,7 @@
         <v>70</v>
       </c>
       <c r="F37" s="11">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1599,7 +1599,7 @@
         <v>74</v>
       </c>
       <c r="F39" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/push.xlsx
+++ b/prix/push.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573844AB-A392-4EBE-B116-D79D882D0B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06685546-14AF-4497-9B13-851DD9FE2C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{37F12267-615D-4EAF-9E58-766BB65D19FA}"/>
   </bookViews>
@@ -882,13 +882,13 @@
         <v>16</v>
       </c>
       <c r="D3" s="10">
-        <v>3.7600000000000002</v>
+        <v>2.89</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="11">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -948,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="11">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1045,7 +1045,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="11">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1099,7 +1099,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="11">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1119,7 +1119,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1179,7 +1179,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="11">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1219,7 +1219,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="11">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1259,7 +1259,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="11">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1319,7 +1319,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="11">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1359,7 +1359,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="11">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1433,13 +1433,13 @@
         <v>93</v>
       </c>
       <c r="D31" s="10">
-        <v>7.36</v>
+        <v>8.49</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>58</v>
       </c>
       <c r="F31" s="11">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1479,7 +1479,7 @@
         <v>62</v>
       </c>
       <c r="F33" s="11">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1519,7 +1519,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1533,13 +1533,13 @@
         <v>97</v>
       </c>
       <c r="D36" s="10">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>68</v>
       </c>
       <c r="F36" s="11">
-        <v>13</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1619,7 +1619,7 @@
         <v>76</v>
       </c>
       <c r="F40" s="11">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
